--- a/artfynd/A 20575-2025 artfynd.xlsx
+++ b/artfynd/A 20575-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ88"/>
+  <dimension ref="A1:AZ90"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6555,10 +6555,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128709188</v>
+        <v>136950265</v>
       </c>
       <c r="B59" t="n">
-        <v>99142</v>
+        <v>99270</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6566,34 +6566,42 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>219847</v>
+        <v>219790</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr"/>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr"/>
+      <c r="K59" t="inlineStr"/>
+      <c r="L59" t="inlineStr"/>
+      <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Höglunda-Öratjärnen (väg 731), Jmt</t>
+          <t>Koviken, Jmt</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>550802</v>
+        <v>550790</v>
       </c>
       <c r="R59" t="n">
-        <v>6998925</v>
+        <v>6998924</v>
       </c>
       <c r="S59" t="n">
         <v>5</v>
@@ -6620,12 +6628,12 @@
       </c>
       <c r="Y59" t="inlineStr">
         <is>
-          <t>2025-06-16</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>2025-06-16</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6634,34 +6642,35 @@
       <c r="AE59" t="b">
         <v>0</v>
       </c>
+      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
       </c>
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Mika Thunell</t>
+          <t>Staffan Fridh</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Magnus Lundin, Mika Thunell</t>
+          <t>Signe Jönsson</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr">
         <is>
-          <t>C250138 Dikesinventering Jämtland 2025</t>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
         </is>
       </c>
       <c r="AZ59" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128709188</t>
+          <t>https://artportalen.se/Sighting/136950265</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128709194</v>
+        <v>128709188</v>
       </c>
       <c r="B60" t="n">
         <v>99142</v>
@@ -6696,10 +6705,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>550777</v>
+        <v>550802</v>
       </c>
       <c r="R60" t="n">
-        <v>6998940</v>
+        <v>6998925</v>
       </c>
       <c r="S60" t="n">
         <v>5</v>
@@ -6751,7 +6760,7 @@
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Mika Thunell, Magnus Lundin</t>
+          <t>Magnus Lundin, Mika Thunell</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr">
@@ -6761,13 +6770,13 @@
       </c>
       <c r="AZ60" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128709194</t>
+          <t>https://artportalen.se/Sighting/128709188</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128709208</v>
+        <v>128709194</v>
       </c>
       <c r="B61" t="n">
         <v>99142</v>
@@ -6802,10 +6811,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>550759</v>
+        <v>550777</v>
       </c>
       <c r="R61" t="n">
-        <v>6998935</v>
+        <v>6998940</v>
       </c>
       <c r="S61" t="n">
         <v>5</v>
@@ -6867,13 +6876,13 @@
       </c>
       <c r="AZ61" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128709208</t>
+          <t>https://artportalen.se/Sighting/128709194</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>128709210</v>
+        <v>128709208</v>
       </c>
       <c r="B62" t="n">
         <v>99142</v>
@@ -6908,10 +6917,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>550762</v>
+        <v>550759</v>
       </c>
       <c r="R62" t="n">
-        <v>6998937</v>
+        <v>6998935</v>
       </c>
       <c r="S62" t="n">
         <v>5</v>
@@ -6973,13 +6982,13 @@
       </c>
       <c r="AZ62" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128709210</t>
+          <t>https://artportalen.se/Sighting/128709208</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>128709216</v>
+        <v>128709210</v>
       </c>
       <c r="B63" t="n">
         <v>99142</v>
@@ -7014,10 +7023,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>550794</v>
+        <v>550762</v>
       </c>
       <c r="R63" t="n">
-        <v>6998930</v>
+        <v>6998937</v>
       </c>
       <c r="S63" t="n">
         <v>5</v>
@@ -7069,7 +7078,7 @@
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Magnus Lundin, Mika Thunell</t>
+          <t>Mika Thunell, Magnus Lundin</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr">
@@ -7079,13 +7088,13 @@
       </c>
       <c r="AZ63" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128709216</t>
+          <t>https://artportalen.se/Sighting/128709210</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>128709221</v>
+        <v>128709216</v>
       </c>
       <c r="B64" t="n">
         <v>99142</v>
@@ -7120,10 +7129,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>550770</v>
+        <v>550794</v>
       </c>
       <c r="R64" t="n">
-        <v>6998942</v>
+        <v>6998930</v>
       </c>
       <c r="S64" t="n">
         <v>5</v>
@@ -7175,7 +7184,7 @@
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Mika Thunell, Magnus Lundin</t>
+          <t>Magnus Lundin, Mika Thunell</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr">
@@ -7185,16 +7194,16 @@
       </c>
       <c r="AZ64" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128709221</t>
+          <t>https://artportalen.se/Sighting/128709216</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>134654433</v>
+        <v>128709221</v>
       </c>
       <c r="B65" t="n">
-        <v>99219</v>
+        <v>99142</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7222,17 +7231,17 @@
       <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Koviken, Jmt</t>
+          <t>Höglunda-Öratjärnen (väg 731), Jmt</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>550788</v>
+        <v>550770</v>
       </c>
       <c r="R65" t="n">
-        <v>6998923</v>
+        <v>6998942</v>
       </c>
       <c r="S65" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7256,12 +7265,12 @@
       </c>
       <c r="Y65" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2025-06-16</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2025-06-16</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7276,24 +7285,28 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Rasmus Viding</t>
+          <t>Mika Thunell</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Rasmus Viding</t>
-        </is>
-      </c>
-      <c r="AY65" t="inlineStr"/>
+          <t>Mika Thunell, Magnus Lundin</t>
+        </is>
+      </c>
+      <c r="AY65" t="inlineStr">
+        <is>
+          <t>C250138 Dikesinventering Jämtland 2025</t>
+        </is>
+      </c>
       <c r="AZ65" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134654433</t>
+          <t>https://artportalen.se/Sighting/128709221</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>134654436</v>
+        <v>134654433</v>
       </c>
       <c r="B66" t="n">
         <v>99219</v>
@@ -7328,10 +7341,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>550735</v>
+        <v>550788</v>
       </c>
       <c r="R66" t="n">
-        <v>6998933</v>
+        <v>6998923</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7389,13 +7402,13 @@
       <c r="AY66" t="inlineStr"/>
       <c r="AZ66" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134654436</t>
+          <t>https://artportalen.se/Sighting/134654433</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>134654439</v>
+        <v>134654436</v>
       </c>
       <c r="B67" t="n">
         <v>99219</v>
@@ -7430,10 +7443,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>550628</v>
+        <v>550735</v>
       </c>
       <c r="R67" t="n">
-        <v>6998976</v>
+        <v>6998933</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7491,13 +7504,13 @@
       <c r="AY67" t="inlineStr"/>
       <c r="AZ67" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134654439</t>
+          <t>https://artportalen.se/Sighting/134654436</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>134654445</v>
+        <v>134654439</v>
       </c>
       <c r="B68" t="n">
         <v>99219</v>
@@ -7532,10 +7545,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>550691</v>
+        <v>550628</v>
       </c>
       <c r="R68" t="n">
-        <v>6998945</v>
+        <v>6998976</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7593,13 +7606,13 @@
       <c r="AY68" t="inlineStr"/>
       <c r="AZ68" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134654445</t>
+          <t>https://artportalen.se/Sighting/134654439</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>134654446</v>
+        <v>134654445</v>
       </c>
       <c r="B69" t="n">
         <v>99219</v>
@@ -7634,10 +7647,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>550695</v>
+        <v>550691</v>
       </c>
       <c r="R69" t="n">
-        <v>6998946</v>
+        <v>6998945</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7695,13 +7708,13 @@
       <c r="AY69" t="inlineStr"/>
       <c r="AZ69" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134654446</t>
+          <t>https://artportalen.se/Sighting/134654445</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>134654452</v>
+        <v>134654446</v>
       </c>
       <c r="B70" t="n">
         <v>99219</v>
@@ -7736,10 +7749,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>550864</v>
+        <v>550695</v>
       </c>
       <c r="R70" t="n">
-        <v>6998911</v>
+        <v>6998946</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7797,13 +7810,13 @@
       <c r="AY70" t="inlineStr"/>
       <c r="AZ70" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134654452</t>
+          <t>https://artportalen.se/Sighting/134654446</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>134654463</v>
+        <v>134654452</v>
       </c>
       <c r="B71" t="n">
         <v>99219</v>
@@ -7838,10 +7851,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>550753</v>
+        <v>550864</v>
       </c>
       <c r="R71" t="n">
-        <v>6998943</v>
+        <v>6998911</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7899,13 +7912,13 @@
       <c r="AY71" t="inlineStr"/>
       <c r="AZ71" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134654463</t>
+          <t>https://artportalen.se/Sighting/134654452</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>134654476</v>
+        <v>134654463</v>
       </c>
       <c r="B72" t="n">
         <v>99219</v>
@@ -7940,10 +7953,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>550760</v>
+        <v>550753</v>
       </c>
       <c r="R72" t="n">
-        <v>6998939</v>
+        <v>6998943</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8001,13 +8014,13 @@
       <c r="AY72" t="inlineStr"/>
       <c r="AZ72" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134654476</t>
+          <t>https://artportalen.se/Sighting/134654463</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>134654478</v>
+        <v>134654476</v>
       </c>
       <c r="B73" t="n">
         <v>99219</v>
@@ -8045,7 +8058,7 @@
         <v>550760</v>
       </c>
       <c r="R73" t="n">
-        <v>6998935</v>
+        <v>6998939</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8103,13 +8116,13 @@
       <c r="AY73" t="inlineStr"/>
       <c r="AZ73" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134654478</t>
+          <t>https://artportalen.se/Sighting/134654476</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>134654480</v>
+        <v>134654478</v>
       </c>
       <c r="B74" t="n">
         <v>99219</v>
@@ -8144,10 +8157,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>550767</v>
+        <v>550760</v>
       </c>
       <c r="R74" t="n">
-        <v>6998933</v>
+        <v>6998935</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8205,13 +8218,13 @@
       <c r="AY74" t="inlineStr"/>
       <c r="AZ74" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134654480</t>
+          <t>https://artportalen.se/Sighting/134654478</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>134654482</v>
+        <v>134654480</v>
       </c>
       <c r="B75" t="n">
         <v>99219</v>
@@ -8246,7 +8259,7 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>550771</v>
+        <v>550767</v>
       </c>
       <c r="R75" t="n">
         <v>6998933</v>
@@ -8307,13 +8320,13 @@
       <c r="AY75" t="inlineStr"/>
       <c r="AZ75" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134654482</t>
+          <t>https://artportalen.se/Sighting/134654480</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>134654484</v>
+        <v>134654482</v>
       </c>
       <c r="B76" t="n">
         <v>99219</v>
@@ -8348,7 +8361,7 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>550775</v>
+        <v>550771</v>
       </c>
       <c r="R76" t="n">
         <v>6998933</v>
@@ -8409,13 +8422,13 @@
       <c r="AY76" t="inlineStr"/>
       <c r="AZ76" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134654484</t>
+          <t>https://artportalen.se/Sighting/134654482</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>134654486</v>
+        <v>134654484</v>
       </c>
       <c r="B77" t="n">
         <v>99219</v>
@@ -8450,10 +8463,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>550779</v>
+        <v>550775</v>
       </c>
       <c r="R77" t="n">
-        <v>6998930</v>
+        <v>6998933</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8511,13 +8524,13 @@
       <c r="AY77" t="inlineStr"/>
       <c r="AZ77" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134654486</t>
+          <t>https://artportalen.se/Sighting/134654484</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>134654489</v>
+        <v>134654486</v>
       </c>
       <c r="B78" t="n">
         <v>99219</v>
@@ -8552,10 +8565,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>550806</v>
+        <v>550779</v>
       </c>
       <c r="R78" t="n">
-        <v>6998928</v>
+        <v>6998930</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8613,13 +8626,13 @@
       <c r="AY78" t="inlineStr"/>
       <c r="AZ78" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134654489</t>
+          <t>https://artportalen.se/Sighting/134654486</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>134654490</v>
+        <v>134654489</v>
       </c>
       <c r="B79" t="n">
         <v>99219</v>
@@ -8654,10 +8667,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>550801</v>
+        <v>550806</v>
       </c>
       <c r="R79" t="n">
-        <v>6998932</v>
+        <v>6998928</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8715,51 +8728,51 @@
       <c r="AY79" t="inlineStr"/>
       <c r="AZ79" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134654490</t>
+          <t>https://artportalen.se/Sighting/134654489</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>133729068</v>
+        <v>134654490</v>
       </c>
       <c r="B80" t="n">
-        <v>99195</v>
+        <v>99219</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>220787</v>
+        <v>219847</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Granliden, Jmt</t>
+          <t>Koviken, Jmt</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>550587</v>
+        <v>550801</v>
       </c>
       <c r="R80" t="n">
-        <v>6998825</v>
+        <v>6998932</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8786,12 +8799,12 @@
       </c>
       <c r="Y80" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -8806,69 +8819,73 @@
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Anders Malmsten</t>
+          <t>Rasmus Viding</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Anders Malmsten</t>
+          <t>Rasmus Viding</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
       <c r="AZ80" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133729068</t>
+          <t>https://artportalen.se/Sighting/134654490</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>133729085</v>
+        <v>136950266</v>
       </c>
       <c r="B81" t="n">
-        <v>99195</v>
+        <v>99377</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>220787</v>
+        <v>219847</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I81" t="inlineStr"/>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="J81" t="inlineStr"/>
       <c r="K81" t="inlineStr"/>
       <c r="L81" t="inlineStr"/>
       <c r="N81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Granliden, Jmt</t>
+          <t>Koviken, Jmt</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>550735</v>
+        <v>550790</v>
       </c>
       <c r="R81" t="n">
-        <v>6998530</v>
+        <v>6998924</v>
       </c>
       <c r="S81" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -8892,17 +8909,12 @@
       </c>
       <c r="Y81" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
-        </is>
-      </c>
-      <c r="AC81" t="inlineStr">
-        <is>
-          <t>på mossig låga över vattnet i dråg</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -8918,24 +8930,28 @@
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Anders Malmsten</t>
+          <t>Staffan Fridh</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Anders Malmsten</t>
-        </is>
-      </c>
-      <c r="AY81" t="inlineStr"/>
+          <t>Signe Jönsson</t>
+        </is>
+      </c>
+      <c r="AY81" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
       <c r="AZ81" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133729085</t>
+          <t>https://artportalen.se/Sighting/136950266</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>133729086</v>
+        <v>133729068</v>
       </c>
       <c r="B82" t="n">
         <v>99195</v>
@@ -8970,10 +8986,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>550739</v>
+        <v>550587</v>
       </c>
       <c r="R82" t="n">
-        <v>6998590</v>
+        <v>6998825</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9031,13 +9047,13 @@
       <c r="AY82" t="inlineStr"/>
       <c r="AZ82" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133729086</t>
+          <t>https://artportalen.se/Sighting/133729068</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>134654427</v>
+        <v>133729085</v>
       </c>
       <c r="B83" t="n">
         <v>99195</v>
@@ -9066,16 +9082,20 @@
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
+      <c r="J83" t="inlineStr"/>
+      <c r="K83" t="inlineStr"/>
+      <c r="L83" t="inlineStr"/>
+      <c r="N83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Koviken, Jmt</t>
+          <t>Granliden, Jmt</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>550700</v>
+        <v>550735</v>
       </c>
       <c r="R83" t="n">
-        <v>6998928</v>
+        <v>6998530</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9102,12 +9122,17 @@
       </c>
       <c r="Y83" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="AC83" t="inlineStr">
+        <is>
+          <t>på mossig låga över vattnet i dråg</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9116,30 +9141,31 @@
       <c r="AE83" t="b">
         <v>0</v>
       </c>
+      <c r="AF83" t="inlineStr"/>
       <c r="AG83" t="b">
         <v>0</v>
       </c>
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Rasmus Viding</t>
+          <t>Anders Malmsten</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Rasmus Viding</t>
+          <t>Anders Malmsten</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
       <c r="AZ83" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134654427</t>
+          <t>https://artportalen.se/Sighting/133729085</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>134654430</v>
+        <v>133729086</v>
       </c>
       <c r="B84" t="n">
         <v>99195</v>
@@ -9170,14 +9196,14 @@
       <c r="I84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Koviken, Jmt</t>
+          <t>Granliden, Jmt</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>550829</v>
+        <v>550739</v>
       </c>
       <c r="R84" t="n">
-        <v>6998830</v>
+        <v>6998590</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9204,12 +9230,12 @@
       </c>
       <c r="Y84" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9224,24 +9250,24 @@
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Rasmus Viding</t>
+          <t>Anders Malmsten</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Rasmus Viding</t>
+          <t>Anders Malmsten</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
       <c r="AZ84" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134654430</t>
+          <t>https://artportalen.se/Sighting/133729086</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>134654431</v>
+        <v>134654427</v>
       </c>
       <c r="B85" t="n">
         <v>99195</v>
@@ -9276,10 +9302,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>550835</v>
+        <v>550700</v>
       </c>
       <c r="R85" t="n">
-        <v>6998837</v>
+        <v>6998928</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9337,51 +9363,51 @@
       <c r="AY85" t="inlineStr"/>
       <c r="AZ85" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134654431</t>
+          <t>https://artportalen.se/Sighting/134654427</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>133729087</v>
+        <v>134654430</v>
       </c>
       <c r="B86" t="n">
-        <v>99217</v>
+        <v>99195</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Granliden, Jmt</t>
+          <t>Koviken, Jmt</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>550719</v>
+        <v>550829</v>
       </c>
       <c r="R86" t="n">
-        <v>6998593</v>
+        <v>6998830</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9408,12 +9434,12 @@
       </c>
       <c r="Y86" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9428,49 +9454,49 @@
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Anders Malmsten</t>
+          <t>Rasmus Viding</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Anders Malmsten</t>
+          <t>Rasmus Viding</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
       <c r="AZ86" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133729087</t>
+          <t>https://artportalen.se/Sighting/134654430</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>134654428</v>
+        <v>134654431</v>
       </c>
       <c r="B87" t="n">
-        <v>99217</v>
+        <v>99195</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9480,10 +9506,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>550682</v>
+        <v>550835</v>
       </c>
       <c r="R87" t="n">
-        <v>6998887</v>
+        <v>6998837</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9541,13 +9567,13 @@
       <c r="AY87" t="inlineStr"/>
       <c r="AZ87" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134654428</t>
+          <t>https://artportalen.se/Sighting/134654431</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>134654429</v>
+        <v>133729087</v>
       </c>
       <c r="B88" t="n">
         <v>99217</v>
@@ -9578,14 +9604,14 @@
       <c r="I88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
-          <t>Koviken, Jmt</t>
+          <t>Granliden, Jmt</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>550698</v>
+        <v>550719</v>
       </c>
       <c r="R88" t="n">
-        <v>6998829</v>
+        <v>6998593</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9612,12 +9638,12 @@
       </c>
       <c r="Y88" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -9632,16 +9658,220 @@
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Rasmus Viding</t>
+          <t>Anders Malmsten</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Rasmus Viding</t>
+          <t>Anders Malmsten</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
       <c r="AZ88" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133729087</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>134654428</v>
+      </c>
+      <c r="B89" t="n">
+        <v>99217</v>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E89" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr"/>
+      <c r="P89" t="inlineStr">
+        <is>
+          <t>Koviken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q89" t="n">
+        <v>550682</v>
+      </c>
+      <c r="R89" t="n">
+        <v>6998887</v>
+      </c>
+      <c r="S89" t="n">
+        <v>10</v>
+      </c>
+      <c r="T89" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U89" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V89" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W89" t="inlineStr">
+        <is>
+          <t>Stugun</t>
+        </is>
+      </c>
+      <c r="Y89" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="AA89" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="AD89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT89" t="inlineStr"/>
+      <c r="AW89" t="inlineStr">
+        <is>
+          <t>Rasmus Viding</t>
+        </is>
+      </c>
+      <c r="AX89" t="inlineStr">
+        <is>
+          <t>Rasmus Viding</t>
+        </is>
+      </c>
+      <c r="AY89" t="inlineStr"/>
+      <c r="AZ89" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134654428</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>134654429</v>
+      </c>
+      <c r="B90" t="n">
+        <v>99217</v>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E90" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr"/>
+      <c r="P90" t="inlineStr">
+        <is>
+          <t>Koviken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q90" t="n">
+        <v>550698</v>
+      </c>
+      <c r="R90" t="n">
+        <v>6998829</v>
+      </c>
+      <c r="S90" t="n">
+        <v>10</v>
+      </c>
+      <c r="T90" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U90" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V90" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W90" t="inlineStr">
+        <is>
+          <t>Stugun</t>
+        </is>
+      </c>
+      <c r="Y90" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="AA90" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="AD90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT90" t="inlineStr"/>
+      <c r="AW90" t="inlineStr">
+        <is>
+          <t>Rasmus Viding</t>
+        </is>
+      </c>
+      <c r="AX90" t="inlineStr">
+        <is>
+          <t>Rasmus Viding</t>
+        </is>
+      </c>
+      <c r="AY90" t="inlineStr"/>
+      <c r="AZ90" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/134654429</t>
         </is>
@@ -9736,6 +9966,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ87" r:id="rId86"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ90" r:id="rId89"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 20575-2025 artfynd.xlsx
+++ b/artfynd/A 20575-2025 artfynd.xlsx
@@ -6558,7 +6558,7 @@
         <v>136950265</v>
       </c>
       <c r="B59" t="n">
-        <v>99270</v>
+        <v>99276</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -8839,7 +8839,7 @@
         <v>136950266</v>
       </c>
       <c r="B81" t="n">
-        <v>99377</v>
+        <v>99383</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>

--- a/artfynd/A 20575-2025 artfynd.xlsx
+++ b/artfynd/A 20575-2025 artfynd.xlsx
@@ -6558,7 +6558,7 @@
         <v>136950265</v>
       </c>
       <c r="B59" t="n">
-        <v>99276</v>
+        <v>99278</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -8839,7 +8839,7 @@
         <v>136950266</v>
       </c>
       <c r="B81" t="n">
-        <v>99383</v>
+        <v>99385</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>

--- a/artfynd/A 20575-2025 artfynd.xlsx
+++ b/artfynd/A 20575-2025 artfynd.xlsx
@@ -6558,7 +6558,7 @@
         <v>136950265</v>
       </c>
       <c r="B59" t="n">
-        <v>99278</v>
+        <v>99279</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -8839,7 +8839,7 @@
         <v>136950266</v>
       </c>
       <c r="B81" t="n">
-        <v>99385</v>
+        <v>99386</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>

--- a/artfynd/A 20575-2025 artfynd.xlsx
+++ b/artfynd/A 20575-2025 artfynd.xlsx
@@ -6558,7 +6558,7 @@
         <v>136950265</v>
       </c>
       <c r="B59" t="n">
-        <v>99279</v>
+        <v>99285</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -8839,7 +8839,7 @@
         <v>136950266</v>
       </c>
       <c r="B81" t="n">
-        <v>99386</v>
+        <v>99392</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>

--- a/artfynd/A 20575-2025 artfynd.xlsx
+++ b/artfynd/A 20575-2025 artfynd.xlsx
@@ -6558,7 +6558,7 @@
         <v>136950265</v>
       </c>
       <c r="B59" t="n">
-        <v>99285</v>
+        <v>99289</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -8839,7 +8839,7 @@
         <v>136950266</v>
       </c>
       <c r="B81" t="n">
-        <v>99392</v>
+        <v>99396</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>

--- a/artfynd/A 20575-2025 artfynd.xlsx
+++ b/artfynd/A 20575-2025 artfynd.xlsx
@@ -6558,7 +6558,7 @@
         <v>136950265</v>
       </c>
       <c r="B59" t="n">
-        <v>99289</v>
+        <v>99291</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -8839,7 +8839,7 @@
         <v>136950266</v>
       </c>
       <c r="B81" t="n">
-        <v>99396</v>
+        <v>99398</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>

--- a/artfynd/A 20575-2025 artfynd.xlsx
+++ b/artfynd/A 20575-2025 artfynd.xlsx
@@ -6558,7 +6558,7 @@
         <v>136950265</v>
       </c>
       <c r="B59" t="n">
-        <v>99291</v>
+        <v>99293</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -8839,7 +8839,7 @@
         <v>136950266</v>
       </c>
       <c r="B81" t="n">
-        <v>99398</v>
+        <v>99400</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>

--- a/artfynd/A 20575-2025 artfynd.xlsx
+++ b/artfynd/A 20575-2025 artfynd.xlsx
@@ -6558,7 +6558,7 @@
         <v>136950265</v>
       </c>
       <c r="B59" t="n">
-        <v>99293</v>
+        <v>99306</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -8839,7 +8839,7 @@
         <v>136950266</v>
       </c>
       <c r="B81" t="n">
-        <v>99400</v>
+        <v>99413</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>

--- a/artfynd/A 20575-2025 artfynd.xlsx
+++ b/artfynd/A 20575-2025 artfynd.xlsx
@@ -6558,7 +6558,7 @@
         <v>136950265</v>
       </c>
       <c r="B59" t="n">
-        <v>99306</v>
+        <v>99308</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -8839,7 +8839,7 @@
         <v>136950266</v>
       </c>
       <c r="B81" t="n">
-        <v>99413</v>
+        <v>99415</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>

--- a/artfynd/A 20575-2025 artfynd.xlsx
+++ b/artfynd/A 20575-2025 artfynd.xlsx
@@ -6558,7 +6558,7 @@
         <v>136950265</v>
       </c>
       <c r="B59" t="n">
-        <v>99308</v>
+        <v>99311</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -8839,7 +8839,7 @@
         <v>136950266</v>
       </c>
       <c r="B81" t="n">
-        <v>99415</v>
+        <v>99418</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>

--- a/artfynd/A 20575-2025 artfynd.xlsx
+++ b/artfynd/A 20575-2025 artfynd.xlsx
@@ -6558,7 +6558,7 @@
         <v>136950265</v>
       </c>
       <c r="B59" t="n">
-        <v>99311</v>
+        <v>99321</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -8839,7 +8839,7 @@
         <v>136950266</v>
       </c>
       <c r="B81" t="n">
-        <v>99418</v>
+        <v>99428</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>

--- a/artfynd/A 20575-2025 artfynd.xlsx
+++ b/artfynd/A 20575-2025 artfynd.xlsx
@@ -6558,7 +6558,7 @@
         <v>136950265</v>
       </c>
       <c r="B59" t="n">
-        <v>99321</v>
+        <v>99322</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -8839,7 +8839,7 @@
         <v>136950266</v>
       </c>
       <c r="B81" t="n">
-        <v>99428</v>
+        <v>99429</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>

--- a/artfynd/A 20575-2025 artfynd.xlsx
+++ b/artfynd/A 20575-2025 artfynd.xlsx
@@ -6558,7 +6558,7 @@
         <v>136950265</v>
       </c>
       <c r="B59" t="n">
-        <v>99322</v>
+        <v>99327</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -8839,7 +8839,7 @@
         <v>136950266</v>
       </c>
       <c r="B81" t="n">
-        <v>99429</v>
+        <v>99434</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>

--- a/artfynd/A 20575-2025 artfynd.xlsx
+++ b/artfynd/A 20575-2025 artfynd.xlsx
@@ -6558,7 +6558,7 @@
         <v>136950265</v>
       </c>
       <c r="B59" t="n">
-        <v>99327</v>
+        <v>99329</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -8839,7 +8839,7 @@
         <v>136950266</v>
       </c>
       <c r="B81" t="n">
-        <v>99434</v>
+        <v>99436</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>

--- a/artfynd/A 20575-2025 artfynd.xlsx
+++ b/artfynd/A 20575-2025 artfynd.xlsx
@@ -6558,7 +6558,7 @@
         <v>136950265</v>
       </c>
       <c r="B59" t="n">
-        <v>99329</v>
+        <v>99335</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -8839,7 +8839,7 @@
         <v>136950266</v>
       </c>
       <c r="B81" t="n">
-        <v>99436</v>
+        <v>99442</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>

--- a/artfynd/A 20575-2025 artfynd.xlsx
+++ b/artfynd/A 20575-2025 artfynd.xlsx
@@ -6558,7 +6558,7 @@
         <v>136950265</v>
       </c>
       <c r="B59" t="n">
-        <v>99335</v>
+        <v>99347</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -8839,7 +8839,7 @@
         <v>136950266</v>
       </c>
       <c r="B81" t="n">
-        <v>99442</v>
+        <v>99454</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>

--- a/artfynd/A 20575-2025 artfynd.xlsx
+++ b/artfynd/A 20575-2025 artfynd.xlsx
@@ -6558,7 +6558,7 @@
         <v>136950265</v>
       </c>
       <c r="B59" t="n">
-        <v>99347</v>
+        <v>99348</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -8839,7 +8839,7 @@
         <v>136950266</v>
       </c>
       <c r="B81" t="n">
-        <v>99454</v>
+        <v>99455</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>

--- a/artfynd/A 20575-2025 artfynd.xlsx
+++ b/artfynd/A 20575-2025 artfynd.xlsx
@@ -6558,7 +6558,7 @@
         <v>136950265</v>
       </c>
       <c r="B59" t="n">
-        <v>99348</v>
+        <v>99351</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -8839,7 +8839,7 @@
         <v>136950266</v>
       </c>
       <c r="B81" t="n">
-        <v>99455</v>
+        <v>99458</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>

--- a/artfynd/A 20575-2025 artfynd.xlsx
+++ b/artfynd/A 20575-2025 artfynd.xlsx
@@ -6558,7 +6558,7 @@
         <v>136950265</v>
       </c>
       <c r="B59" t="n">
-        <v>99351</v>
+        <v>99352</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -8839,7 +8839,7 @@
         <v>136950266</v>
       </c>
       <c r="B81" t="n">
-        <v>99458</v>
+        <v>99459</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>

--- a/artfynd/A 20575-2025 artfynd.xlsx
+++ b/artfynd/A 20575-2025 artfynd.xlsx
@@ -6558,7 +6558,7 @@
         <v>136950265</v>
       </c>
       <c r="B59" t="n">
-        <v>99352</v>
+        <v>99355</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -8839,7 +8839,7 @@
         <v>136950266</v>
       </c>
       <c r="B81" t="n">
-        <v>99459</v>
+        <v>99462</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
